--- a/3DGame202509/その他作業/コスト表.xlsx
+++ b/3DGame202509/その他作業/コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\藤原 冬志\Desktop\GitHub\3DGame202509\3DGame202509\その他作業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D79C83-FC41-4A8B-A97E-D01D08DFB750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A31445-F40A-487C-A120-113C786F1DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="2805" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="405" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="3" r:id="rId1"/>
@@ -344,16 +344,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・雑魚3種</t>
-    <rPh sb="1" eb="3">
-      <t>ザコ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>　ー　リザルト画面</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -588,6 +578,16 @@
   </si>
   <si>
     <t>　ー　キャラモーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・雑魚2種</t>
+    <rPh sb="1" eb="3">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シュ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1077,7 +1077,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <f>SUM(コスト表!E3:E85)</f>
@@ -1086,32 +1086,32 @@
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <f>SUMIF(コスト表!F3:F85,"完了",コスト表!E3:E85)</f>
-        <v>15.5</v>
+        <v>37.25</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="B4" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="15">
         <f ca="1">NETWORKDAYS(C5,C6)</f>
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D4" s="16">
         <f ca="1" xml:space="preserve"> C3 / C4</f>
-        <v>0.67391304347826086</v>
+        <v>1.0347222222222223</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1">
         <f>DATE(2025,5,26)</f>
@@ -1120,24 +1120,24 @@
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45833</v>
+        <v>45852</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
         <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="1">
         <f>DATE(2025,7,23)</f>
@@ -1145,16 +1145,16 @@
       </c>
       <c r="D9" s="15">
         <f ca="1">NETWORKDAYS(TODAY(),C9)</f>
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E9" s="16">
         <f ca="1">($C$2 - $C$3) / D9</f>
-        <v>2.1309523809523809</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="1">
         <f>DATE(2025,8,1)</f>
@@ -1162,16 +1162,16 @@
       </c>
       <c r="D10" s="15">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E10" s="16">
         <f ca="1">($C$2 - $C$3) / D10</f>
-        <v>1.5982142857142858</v>
+        <v>1.5333333333333334</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="1">
         <f>DATE(2025,8,22)</f>
@@ -1179,61 +1179,61 @@
       </c>
       <c r="D11" s="15">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E11" s="16">
         <f ca="1">($C$2 - $C$3) / D11</f>
-        <v>1.0406976744186047</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1284,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:6">
@@ -1301,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -1383,7 +1383,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>3</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>3</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>0.5</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -1455,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="2:6">
@@ -1472,7 +1472,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="2:6">
@@ -1498,7 +1498,7 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -1515,12 +1515,12 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>3</v>
@@ -1532,12 +1532,12 @@
         <v>0.5</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>3</v>
@@ -1549,7 +1549,7 @@
         <v>0.5</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="2:6">
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -1583,7 +1583,7 @@
         <v>0.5</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:6">
@@ -1600,7 +1600,7 @@
         <v>1.5</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -1617,7 +1617,7 @@
         <v>0.25</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -1677,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -1694,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -1711,7 +1711,7 @@
         <v>0.25</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -1728,12 +1728,12 @@
         <v>0.25</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="6" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -1797,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="2:6">
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="2:6">
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="2:6">
@@ -1848,7 +1848,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="2:6">
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="2:6">
@@ -1891,7 +1891,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="2:6">
@@ -1908,7 +1908,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="2:6">
@@ -1925,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="2:6">
@@ -2045,12 +2045,12 @@
         <v>1.5</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>2</v>
@@ -2122,7 +2122,7 @@
         <v>0.5</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="2:6">
@@ -2139,7 +2139,7 @@
         <v>0.25</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -2156,7 +2156,7 @@
         <v>0.5</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="2:6">

--- a/3DGame202509/その他作業/コスト表.xlsx
+++ b/3DGame202509/その他作業/コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\藤原 冬志\Desktop\GitHub\3DGame202509\3DGame202509\その他作業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A31445-F40A-487C-A120-113C786F1DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1CB8BC-7675-4505-8E1A-7F6A317A8671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="405" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="1590" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="3" r:id="rId1"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C3">
         <f>SUMIF(コスト表!F3:F85,"完了",コスト表!E3:E85)</f>
-        <v>37.25</v>
+        <v>39.25</v>
       </c>
       <c r="D3" t="s">
         <v>75</v>
@@ -1102,11 +1102,11 @@
       </c>
       <c r="C4" s="15">
         <f ca="1">NETWORKDAYS(C5,C6)</f>
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D4" s="16">
         <f ca="1" xml:space="preserve"> C3 / C4</f>
-        <v>1.0347222222222223</v>
+        <v>0.91279069767441856</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45852</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -1145,11 +1145,11 @@
       </c>
       <c r="D9" s="15">
         <f ca="1">NETWORKDAYS(TODAY(),C9)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E9" s="16">
         <f ca="1">($C$2 - $C$3) / D9</f>
-        <v>2.875</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -1162,11 +1162,11 @@
       </c>
       <c r="D10" s="15">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E10" s="16">
         <f ca="1">($C$2 - $C$3) / D10</f>
-        <v>1.5333333333333334</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -1179,11 +1179,11 @@
       </c>
       <c r="D11" s="15">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E11" s="16">
         <f ca="1">($C$2 - $C$3) / D11</f>
-        <v>0.76666666666666672</v>
+        <v>0.91304347826086951</v>
       </c>
     </row>
     <row r="13" spans="2:5">
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="2:6">
